--- a/运单段码对照表.xlsx
+++ b/运单段码对照表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="634">
   <si>
     <t>运单号</t>
   </si>
@@ -227,6 +227,9 @@
     <t>JDM000002927602</t>
   </si>
   <si>
+    <t>JDM000004661711</t>
+  </si>
+  <si>
     <t>JDM000001749955</t>
   </si>
   <si>
@@ -686,6 +689,9 @@
     <t>JDM000000040844</t>
   </si>
   <si>
+    <t>JDM000001227546</t>
+  </si>
+  <si>
     <t>JDM000004884160</t>
   </si>
   <si>
@@ -860,9 +866,15 @@
     <t>JDM000002280948</t>
   </si>
   <si>
+    <t>JDM000000206485</t>
+  </si>
+  <si>
     <t>JDM000003557138</t>
   </si>
   <si>
+    <t>JDM000002464693</t>
+  </si>
+  <si>
     <t>JDM000002787775</t>
   </si>
   <si>
@@ -1022,6 +1034,9 @@
     <t>JDM000001867713</t>
   </si>
   <si>
+    <t>JDM000001036517</t>
+  </si>
+  <si>
     <t>JDM000004943043</t>
   </si>
   <si>
@@ -1455,6 +1470,9 @@
   </si>
   <si>
     <t>JDM000004064918</t>
+  </si>
+  <si>
+    <t>JDM000004572242</t>
   </si>
   <si>
     <t>JDM000002465182</t>
@@ -1923,7 +1941,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1955,6 +1973,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2466,16 +2491,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2484,119 +2506,122 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2610,6 +2635,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3137,9 +3168,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B601"/>
+  <dimension ref="A1:B607"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
+    <col min="1" max="1" width="26.125" customWidth="1"/>
     <col min="2" max="2" width="34.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3523,8 +3555,8 @@
       <c r="A48" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>19</v>
+      <c r="B48" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -3532,7 +3564,7 @@
         <v>67</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3540,7 +3572,7 @@
         <v>68</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3548,15 +3580,15 @@
         <v>69</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B52" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -3564,7 +3596,7 @@
         <v>72</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3572,7 +3604,7 @@
         <v>73</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -3580,7 +3612,7 @@
         <v>74</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -3588,7 +3620,7 @@
         <v>75</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -3596,7 +3628,7 @@
         <v>76</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -3604,7 +3636,7 @@
         <v>77</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3612,7 +3644,7 @@
         <v>78</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -3620,15 +3652,15 @@
         <v>79</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -3636,7 +3668,7 @@
         <v>82</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -3644,7 +3676,7 @@
         <v>83</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -3652,7 +3684,7 @@
         <v>84</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -3660,7 +3692,7 @@
         <v>85</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -3668,7 +3700,7 @@
         <v>86</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -3676,7 +3708,7 @@
         <v>87</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -3684,7 +3716,7 @@
         <v>88</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -3692,7 +3724,7 @@
         <v>89</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -3700,15 +3732,15 @@
         <v>90</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B71" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -3716,7 +3748,7 @@
         <v>93</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -3724,7 +3756,7 @@
         <v>94</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -3732,7 +3764,7 @@
         <v>95</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -3740,7 +3772,7 @@
         <v>96</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3748,7 +3780,7 @@
         <v>97</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -3764,7 +3796,7 @@
         <v>99</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>91</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -3772,7 +3804,7 @@
         <v>100</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -3780,7 +3812,7 @@
         <v>101</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -3788,7 +3820,7 @@
         <v>102</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -3796,7 +3828,7 @@
         <v>103</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -3804,7 +3836,7 @@
         <v>104</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -3812,7 +3844,7 @@
         <v>105</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -3820,7 +3852,7 @@
         <v>106</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -3828,7 +3860,7 @@
         <v>107</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -3836,7 +3868,7 @@
         <v>108</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -3844,7 +3876,7 @@
         <v>109</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -3852,7 +3884,7 @@
         <v>110</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -3860,7 +3892,7 @@
         <v>111</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -3868,7 +3900,7 @@
         <v>112</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -3876,7 +3908,7 @@
         <v>113</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -3884,7 +3916,7 @@
         <v>114</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -3892,7 +3924,7 @@
         <v>115</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -3900,7 +3932,7 @@
         <v>116</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -3908,7 +3940,7 @@
         <v>117</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -3916,7 +3948,7 @@
         <v>118</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -3924,7 +3956,7 @@
         <v>119</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -3932,7 +3964,7 @@
         <v>120</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -3940,7 +3972,7 @@
         <v>121</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -3948,7 +3980,7 @@
         <v>122</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3956,7 +3988,7 @@
         <v>123</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -3964,7 +3996,7 @@
         <v>124</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -3972,7 +4004,7 @@
         <v>125</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -3980,7 +4012,7 @@
         <v>126</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -3988,7 +4020,7 @@
         <v>127</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -3996,7 +4028,7 @@
         <v>128</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -4004,7 +4036,7 @@
         <v>129</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -4012,7 +4044,7 @@
         <v>130</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -4020,7 +4052,7 @@
         <v>131</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -4028,7 +4060,7 @@
         <v>132</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -4036,7 +4068,7 @@
         <v>133</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -4044,7 +4076,7 @@
         <v>134</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -4052,7 +4084,7 @@
         <v>135</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -4060,7 +4092,7 @@
         <v>136</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -4068,7 +4100,7 @@
         <v>137</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -4076,7 +4108,7 @@
         <v>138</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -4084,7 +4116,7 @@
         <v>139</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -4092,7 +4124,7 @@
         <v>140</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -4100,7 +4132,7 @@
         <v>141</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -4108,7 +4140,7 @@
         <v>142</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -4116,7 +4148,7 @@
         <v>143</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>60</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -4124,7 +4156,7 @@
         <v>144</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -4132,7 +4164,7 @@
         <v>145</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -4148,7 +4180,7 @@
         <v>147</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -4156,7 +4188,7 @@
         <v>148</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -4164,7 +4196,7 @@
         <v>149</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -4172,7 +4204,7 @@
         <v>150</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -4180,7 +4212,7 @@
         <v>151</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -4188,7 +4220,7 @@
         <v>152</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -4196,7 +4228,7 @@
         <v>153</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -4204,7 +4236,7 @@
         <v>154</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -4212,7 +4244,7 @@
         <v>155</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -4220,7 +4252,7 @@
         <v>156</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -4228,7 +4260,7 @@
         <v>157</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -4236,7 +4268,7 @@
         <v>158</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -4244,15 +4276,15 @@
         <v>159</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B139" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -4260,7 +4292,7 @@
         <v>162</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -4268,7 +4300,7 @@
         <v>163</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -4276,7 +4308,7 @@
         <v>164</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -4284,7 +4316,7 @@
         <v>165</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -4292,7 +4324,7 @@
         <v>166</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -4300,7 +4332,7 @@
         <v>167</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -4308,7 +4340,7 @@
         <v>168</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>46</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -4316,7 +4348,7 @@
         <v>169</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -4324,7 +4356,7 @@
         <v>170</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -4332,7 +4364,7 @@
         <v>171</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -4340,7 +4372,7 @@
         <v>172</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -4348,7 +4380,7 @@
         <v>173</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -4356,7 +4388,7 @@
         <v>174</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -4364,7 +4396,7 @@
         <v>175</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -4372,7 +4404,7 @@
         <v>176</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -4380,7 +4412,7 @@
         <v>177</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -4388,7 +4420,7 @@
         <v>178</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -4396,7 +4428,7 @@
         <v>179</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -4404,7 +4436,7 @@
         <v>180</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -4412,7 +4444,7 @@
         <v>181</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -4420,7 +4452,7 @@
         <v>182</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -4428,7 +4460,7 @@
         <v>183</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -4444,7 +4476,7 @@
         <v>185</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -4452,7 +4484,7 @@
         <v>186</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -4460,7 +4492,7 @@
         <v>187</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -4468,7 +4500,7 @@
         <v>188</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -4476,15 +4508,15 @@
         <v>189</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>190</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B168" s="4" t="s">
         <v>191</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -4492,7 +4524,7 @@
         <v>192</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -4508,7 +4540,7 @@
         <v>194</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -4516,7 +4548,7 @@
         <v>195</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -4524,7 +4556,7 @@
         <v>196</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -4532,7 +4564,7 @@
         <v>197</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -4540,7 +4572,7 @@
         <v>198</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -4548,7 +4580,7 @@
         <v>199</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -4556,7 +4588,7 @@
         <v>200</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -4564,7 +4596,7 @@
         <v>201</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -4572,7 +4604,7 @@
         <v>202</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -4588,7 +4620,7 @@
         <v>204</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -4596,7 +4628,7 @@
         <v>205</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -4604,7 +4636,7 @@
         <v>206</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -4612,15 +4644,15 @@
         <v>207</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B185" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="B185" s="4" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -4628,7 +4660,7 @@
         <v>210</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -4636,7 +4668,7 @@
         <v>211</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -4644,7 +4676,7 @@
         <v>212</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -4652,7 +4684,7 @@
         <v>213</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>190</v>
+        <v>53</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -4660,7 +4692,7 @@
         <v>214</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>8</v>
+        <v>191</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -4668,7 +4700,7 @@
         <v>215</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>208</v>
+        <v>8</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -4676,7 +4708,7 @@
         <v>216</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>16</v>
+        <v>209</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -4684,7 +4716,7 @@
         <v>217</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -4692,7 +4724,7 @@
         <v>218</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>208</v>
+        <v>19</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -4700,15 +4732,15 @@
         <v>219</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>14</v>
+        <v>209</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B196" s="4" t="s">
-        <v>190</v>
+      <c r="B196" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -4716,7 +4748,7 @@
         <v>221</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -4724,7 +4756,7 @@
         <v>222</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -4732,7 +4764,7 @@
         <v>223</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -4740,7 +4772,7 @@
         <v>224</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -4748,7 +4780,7 @@
         <v>225</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -4756,7 +4788,7 @@
         <v>226</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -4764,7 +4796,7 @@
         <v>227</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -4772,7 +4804,7 @@
         <v>228</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -4780,7 +4812,7 @@
         <v>229</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -4788,7 +4820,7 @@
         <v>230</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -4796,7 +4828,7 @@
         <v>231</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -4804,7 +4836,7 @@
         <v>232</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -4812,7 +4844,7 @@
         <v>233</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -4820,7 +4852,7 @@
         <v>234</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -4828,7 +4860,7 @@
         <v>235</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -4836,7 +4868,7 @@
         <v>236</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -4844,7 +4876,7 @@
         <v>237</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -4852,7 +4884,7 @@
         <v>238</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -4860,7 +4892,7 @@
         <v>239</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -4868,7 +4900,7 @@
         <v>240</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -4876,7 +4908,7 @@
         <v>241</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -4884,7 +4916,7 @@
         <v>242</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -4892,23 +4924,23 @@
         <v>243</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>244</v>
+        <v>14</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B221" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="B221" s="4" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -4916,7 +4948,7 @@
         <v>247</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -4924,7 +4956,7 @@
         <v>248</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -4932,7 +4964,7 @@
         <v>249</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -4940,7 +4972,7 @@
         <v>250</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -4948,7 +4980,7 @@
         <v>251</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -4956,7 +4988,7 @@
         <v>252</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -4964,7 +4996,7 @@
         <v>253</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -4972,7 +5004,7 @@
         <v>254</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -4980,7 +5012,7 @@
         <v>255</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -4988,7 +5020,7 @@
         <v>256</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -4996,7 +5028,7 @@
         <v>257</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -5004,7 +5036,7 @@
         <v>258</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>190</v>
+        <v>14</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -5012,7 +5044,7 @@
         <v>259</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -5020,7 +5052,7 @@
         <v>260</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>46</v>
+        <v>191</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -5028,7 +5060,7 @@
         <v>261</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -5036,7 +5068,7 @@
         <v>262</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -5044,7 +5076,7 @@
         <v>263</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -5052,7 +5084,7 @@
         <v>264</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -5060,7 +5092,7 @@
         <v>265</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -5068,7 +5100,7 @@
         <v>266</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -5076,7 +5108,7 @@
         <v>267</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -5084,7 +5116,7 @@
         <v>268</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -5092,7 +5124,7 @@
         <v>269</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -5100,7 +5132,7 @@
         <v>270</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -5108,7 +5140,7 @@
         <v>271</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -5116,7 +5148,7 @@
         <v>272</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -5124,7 +5156,7 @@
         <v>273</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -5132,7 +5164,7 @@
         <v>274</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -5140,7 +5172,7 @@
         <v>275</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -5148,7 +5180,7 @@
         <v>276</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -5156,7 +5188,7 @@
         <v>277</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -5164,7 +5196,7 @@
         <v>278</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -5172,7 +5204,7 @@
         <v>279</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -5180,15 +5212,15 @@
         <v>280</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B256" s="4" t="s">
-        <v>34</v>
+      <c r="B256" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -5196,7 +5228,7 @@
         <v>282</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -5204,7 +5236,7 @@
         <v>283</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -5212,7 +5244,7 @@
         <v>284</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -5220,7 +5252,7 @@
         <v>285</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -5228,7 +5260,7 @@
         <v>286</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -5236,7 +5268,7 @@
         <v>287</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -5244,7 +5276,7 @@
         <v>288</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -5252,7 +5284,7 @@
         <v>289</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -5260,7 +5292,7 @@
         <v>290</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -5268,7 +5300,7 @@
         <v>291</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -5284,7 +5316,7 @@
         <v>293</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -5292,7 +5324,7 @@
         <v>294</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -5300,7 +5332,7 @@
         <v>295</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -5308,7 +5340,7 @@
         <v>296</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -5316,7 +5348,7 @@
         <v>297</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -5324,7 +5356,7 @@
         <v>298</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -5332,7 +5364,7 @@
         <v>299</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>91</v>
+        <v>209</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -5348,7 +5380,7 @@
         <v>301</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -5356,7 +5388,7 @@
         <v>302</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -5364,7 +5396,7 @@
         <v>303</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -5372,7 +5404,7 @@
         <v>304</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -5380,7 +5412,7 @@
         <v>305</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -5388,7 +5420,7 @@
         <v>306</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -5396,7 +5428,7 @@
         <v>307</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -5404,7 +5436,7 @@
         <v>308</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -5412,39 +5444,39 @@
         <v>309</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>310</v>
+        <v>81</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B288" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="B288" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -5452,7 +5484,7 @@
         <v>315</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -5468,7 +5500,7 @@
         <v>317</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -5476,7 +5508,7 @@
         <v>318</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -5484,7 +5516,7 @@
         <v>319</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -5492,7 +5524,7 @@
         <v>320</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -5500,7 +5532,7 @@
         <v>321</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -5508,7 +5540,7 @@
         <v>322</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -5516,7 +5548,7 @@
         <v>323</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -5524,7 +5556,7 @@
         <v>324</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -5532,7 +5564,7 @@
         <v>325</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -5548,7 +5580,7 @@
         <v>327</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -5556,7 +5588,7 @@
         <v>328</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -5564,7 +5596,7 @@
         <v>329</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -5580,7 +5612,7 @@
         <v>331</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -5588,7 +5620,7 @@
         <v>332</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -5596,7 +5628,7 @@
         <v>333</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>3</v>
+        <v>71</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -5604,7 +5636,7 @@
         <v>334</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -5612,7 +5644,7 @@
         <v>335</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -5620,7 +5652,7 @@
         <v>336</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>80</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -5628,7 +5660,7 @@
         <v>337</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -5636,7 +5668,7 @@
         <v>338</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -5644,7 +5676,7 @@
         <v>339</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -5652,7 +5684,7 @@
         <v>340</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -5660,7 +5692,7 @@
         <v>341</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -5676,7 +5708,7 @@
         <v>343</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -5684,7 +5716,7 @@
         <v>344</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -5692,7 +5724,7 @@
         <v>345</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -5700,7 +5732,7 @@
         <v>346</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -5708,7 +5740,7 @@
         <v>347</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -5716,7 +5748,7 @@
         <v>348</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -5724,7 +5756,7 @@
         <v>349</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -5732,7 +5764,7 @@
         <v>350</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -5740,7 +5772,7 @@
         <v>351</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -5748,7 +5780,7 @@
         <v>352</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -5756,7 +5788,7 @@
         <v>353</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -5772,7 +5804,7 @@
         <v>355</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -5780,7 +5812,7 @@
         <v>356</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -5788,7 +5820,7 @@
         <v>357</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>91</v>
+        <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -5796,7 +5828,7 @@
         <v>358</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -5804,7 +5836,7 @@
         <v>359</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -5812,7 +5844,7 @@
         <v>360</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -5820,7 +5852,7 @@
         <v>361</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>3</v>
+        <v>81</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -5828,7 +5860,7 @@
         <v>362</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -5836,7 +5868,7 @@
         <v>363</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -5844,7 +5876,7 @@
         <v>364</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -5852,7 +5884,7 @@
         <v>365</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>190</v>
+        <v>25</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -5860,7 +5892,7 @@
         <v>366</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -5868,7 +5900,7 @@
         <v>367</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -5876,7 +5908,7 @@
         <v>368</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -5884,7 +5916,7 @@
         <v>369</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -5892,7 +5924,7 @@
         <v>370</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -5900,7 +5932,7 @@
         <v>371</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -5908,7 +5940,7 @@
         <v>372</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -5916,7 +5948,7 @@
         <v>373</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -5924,7 +5956,7 @@
         <v>374</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -5932,7 +5964,7 @@
         <v>375</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -5940,7 +5972,7 @@
         <v>376</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -5948,7 +5980,7 @@
         <v>377</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -5956,7 +5988,7 @@
         <v>378</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -5964,7 +5996,7 @@
         <v>379</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -5972,7 +6004,7 @@
         <v>380</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -5980,7 +6012,7 @@
         <v>381</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -5988,7 +6020,7 @@
         <v>382</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -5996,7 +6028,7 @@
         <v>383</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -6004,7 +6036,7 @@
         <v>384</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -6012,7 +6044,7 @@
         <v>385</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -6020,7 +6052,7 @@
         <v>386</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -6028,7 +6060,7 @@
         <v>387</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -6036,7 +6068,7 @@
         <v>388</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>53</v>
+        <v>3</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -6044,7 +6076,7 @@
         <v>389</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -6052,7 +6084,7 @@
         <v>390</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -6060,7 +6092,7 @@
         <v>391</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -6068,7 +6100,7 @@
         <v>392</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -6076,7 +6108,7 @@
         <v>393</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -6108,7 +6140,7 @@
         <v>397</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -6116,7 +6148,7 @@
         <v>398</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -6124,7 +6156,7 @@
         <v>399</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -6132,7 +6164,7 @@
         <v>400</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -6148,7 +6180,7 @@
         <v>402</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -6156,7 +6188,7 @@
         <v>403</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -6164,7 +6196,7 @@
         <v>404</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>12</v>
+        <v>209</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -6172,7 +6204,7 @@
         <v>405</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="380" spans="1:2">
@@ -6180,7 +6212,7 @@
         <v>406</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>190</v>
+        <v>19</v>
       </c>
     </row>
     <row r="381" spans="1:2">
@@ -6188,7 +6220,7 @@
         <v>407</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="382" spans="1:2">
@@ -6196,7 +6228,7 @@
         <v>408</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="383" spans="1:2">
@@ -6204,7 +6236,7 @@
         <v>409</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="384" spans="1:2">
@@ -6212,7 +6244,7 @@
         <v>410</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385" spans="1:2">
@@ -6220,7 +6252,7 @@
         <v>411</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="386" spans="1:2">
@@ -6228,7 +6260,7 @@
         <v>412</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>80</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387" spans="1:2">
@@ -6236,7 +6268,7 @@
         <v>413</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="388" spans="1:2">
@@ -6244,7 +6276,7 @@
         <v>414</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="389" spans="1:2">
@@ -6268,7 +6300,7 @@
         <v>417</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
     </row>
     <row r="392" spans="1:2">
@@ -6276,7 +6308,7 @@
         <v>418</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="393" spans="1:2">
@@ -6284,7 +6316,7 @@
         <v>419</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>190</v>
+        <v>21</v>
       </c>
     </row>
     <row r="394" spans="1:2">
@@ -6292,7 +6324,7 @@
         <v>420</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="395" spans="1:2">
@@ -6300,7 +6332,7 @@
         <v>421</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="396" spans="1:2">
@@ -6308,7 +6340,7 @@
         <v>422</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="397" spans="1:2">
@@ -6316,7 +6348,7 @@
         <v>423</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="398" spans="1:2">
@@ -6324,7 +6356,7 @@
         <v>424</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>16</v>
+        <v>191</v>
       </c>
     </row>
     <row r="399" spans="1:2">
@@ -6332,7 +6364,7 @@
         <v>425</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="400" spans="1:2">
@@ -6340,7 +6372,7 @@
         <v>426</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="401" spans="1:2">
@@ -6348,7 +6380,7 @@
         <v>427</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="402" spans="1:2">
@@ -6356,7 +6388,7 @@
         <v>428</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="403" spans="1:2">
@@ -6364,7 +6396,7 @@
         <v>429</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="404" spans="1:2">
@@ -6372,7 +6404,7 @@
         <v>430</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="405" spans="1:2">
@@ -6380,7 +6412,7 @@
         <v>431</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="406" spans="1:2">
@@ -6388,7 +6420,7 @@
         <v>432</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="407" spans="1:2">
@@ -6396,7 +6428,7 @@
         <v>433</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>3</v>
+        <v>71</v>
       </c>
     </row>
     <row r="408" spans="1:2">
@@ -6412,7 +6444,7 @@
         <v>435</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
     </row>
     <row r="410" spans="1:2">
@@ -6420,7 +6452,7 @@
         <v>436</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="411" spans="1:2">
@@ -6428,7 +6460,7 @@
         <v>437</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="412" spans="1:2">
@@ -6436,7 +6468,7 @@
         <v>438</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413" spans="1:2">
@@ -6444,7 +6476,7 @@
         <v>439</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
     </row>
     <row r="414" spans="1:2">
@@ -6452,7 +6484,7 @@
         <v>440</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
     </row>
     <row r="415" spans="1:2">
@@ -6460,7 +6492,7 @@
         <v>441</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
     </row>
     <row r="416" spans="1:2">
@@ -6468,7 +6500,7 @@
         <v>442</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417" spans="1:2">
@@ -6484,7 +6516,7 @@
         <v>444</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="419" spans="1:2">
@@ -6492,7 +6524,7 @@
         <v>445</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="420" spans="1:2">
@@ -6500,7 +6532,7 @@
         <v>446</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>190</v>
+        <v>92</v>
       </c>
     </row>
     <row r="421" spans="1:2">
@@ -6508,7 +6540,7 @@
         <v>447</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="422" spans="1:2">
@@ -6516,7 +6548,7 @@
         <v>448</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="423" spans="1:2">
@@ -6524,7 +6556,7 @@
         <v>449</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>208</v>
+        <v>60</v>
       </c>
     </row>
     <row r="424" spans="1:2">
@@ -6532,7 +6564,7 @@
         <v>450</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="425" spans="1:2">
@@ -6540,7 +6572,7 @@
         <v>451</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="426" spans="1:2">
@@ -6548,7 +6580,7 @@
         <v>452</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
     </row>
     <row r="427" spans="1:2">
@@ -6556,7 +6588,7 @@
         <v>453</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="428" spans="1:2">
@@ -6564,7 +6596,7 @@
         <v>454</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>48</v>
+        <v>209</v>
       </c>
     </row>
     <row r="429" spans="1:2">
@@ -6572,7 +6604,7 @@
         <v>455</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="430" spans="1:2">
@@ -6580,7 +6612,7 @@
         <v>456</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="431" spans="1:2">
@@ -6588,7 +6620,7 @@
         <v>457</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
     </row>
     <row r="432" spans="1:2">
@@ -6596,7 +6628,7 @@
         <v>458</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="433" spans="1:2">
@@ -6604,7 +6636,7 @@
         <v>459</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="434" spans="1:2">
@@ -6612,7 +6644,7 @@
         <v>460</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="435" spans="1:2">
@@ -6620,7 +6652,7 @@
         <v>461</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="436" spans="1:2">
@@ -6628,7 +6660,7 @@
         <v>462</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="437" spans="1:2">
@@ -6644,7 +6676,7 @@
         <v>464</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="439" spans="1:2">
@@ -6652,7 +6684,7 @@
         <v>465</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="440" spans="1:2">
@@ -6660,7 +6692,7 @@
         <v>466</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="441" spans="1:2">
@@ -6668,7 +6700,7 @@
         <v>467</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="442" spans="1:2">
@@ -6676,7 +6708,7 @@
         <v>468</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="443" spans="1:2">
@@ -6684,7 +6716,7 @@
         <v>469</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
     </row>
     <row r="444" spans="1:2">
@@ -6692,7 +6724,7 @@
         <v>470</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="445" spans="1:2">
@@ -6700,7 +6732,7 @@
         <v>471</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="446" spans="1:2">
@@ -6708,7 +6740,7 @@
         <v>472</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
     </row>
     <row r="447" spans="1:2">
@@ -6716,7 +6748,7 @@
         <v>473</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
     </row>
     <row r="448" spans="1:2">
@@ -6724,7 +6756,7 @@
         <v>474</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>160</v>
+        <v>53</v>
       </c>
     </row>
     <row r="449" spans="1:2">
@@ -6732,7 +6764,7 @@
         <v>475</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="450" spans="1:2">
@@ -6740,7 +6772,7 @@
         <v>476</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="451" spans="1:2">
@@ -6748,7 +6780,7 @@
         <v>477</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
     </row>
     <row r="452" spans="1:2">
@@ -6764,7 +6796,7 @@
         <v>479</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>3</v>
+        <v>161</v>
       </c>
     </row>
     <row r="454" spans="1:2">
@@ -6772,15 +6804,15 @@
         <v>480</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
     </row>
     <row r="455" spans="1:2">
       <c r="A455" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="B455" s="4" t="s">
-        <v>3</v>
+      <c r="B455" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="456" spans="1:2">
@@ -6788,7 +6820,7 @@
         <v>482</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="457" spans="1:2">
@@ -6796,7 +6828,7 @@
         <v>483</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="458" spans="1:2">
@@ -6804,7 +6836,7 @@
         <v>484</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="459" spans="1:2">
@@ -6820,7 +6852,7 @@
         <v>486</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>3</v>
+        <v>92</v>
       </c>
     </row>
     <row r="461" spans="1:2">
@@ -6828,7 +6860,7 @@
         <v>487</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="462" spans="1:2">
@@ -6836,7 +6868,7 @@
         <v>488</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>60</v>
+        <v>3</v>
       </c>
     </row>
     <row r="463" spans="1:2">
@@ -6844,7 +6876,7 @@
         <v>489</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="464" spans="1:2">
@@ -6852,7 +6884,7 @@
         <v>490</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>34</v>
+        <v>3</v>
       </c>
     </row>
     <row r="465" spans="1:2">
@@ -6860,7 +6892,7 @@
         <v>491</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -6868,7 +6900,7 @@
         <v>492</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -6876,7 +6908,7 @@
         <v>493</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -6884,7 +6916,7 @@
         <v>494</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -6892,7 +6924,7 @@
         <v>495</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -6900,7 +6932,7 @@
         <v>496</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -6916,7 +6948,7 @@
         <v>498</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -6924,7 +6956,7 @@
         <v>499</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -6932,7 +6964,7 @@
         <v>500</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -6940,7 +6972,7 @@
         <v>501</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -6948,7 +6980,7 @@
         <v>502</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="477" spans="1:2">
@@ -6956,7 +6988,7 @@
         <v>503</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="478" spans="1:2">
@@ -6964,7 +6996,7 @@
         <v>504</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="479" spans="1:2">
@@ -6972,7 +7004,7 @@
         <v>505</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="480" spans="1:2">
@@ -6980,7 +7012,7 @@
         <v>506</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
     </row>
     <row r="481" spans="1:2">
@@ -6988,7 +7020,7 @@
         <v>507</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="482" spans="1:2">
@@ -6996,7 +7028,7 @@
         <v>508</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="483" spans="1:2">
@@ -7004,7 +7036,7 @@
         <v>509</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="484" spans="1:2">
@@ -7012,7 +7044,7 @@
         <v>510</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="485" spans="1:2">
@@ -7020,7 +7052,7 @@
         <v>511</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="486" spans="1:2">
@@ -7028,7 +7060,7 @@
         <v>512</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>208</v>
+        <v>81</v>
       </c>
     </row>
     <row r="487" spans="1:2">
@@ -7036,7 +7068,7 @@
         <v>513</v>
       </c>
       <c r="B487" s="4" t="s">
-        <v>60</v>
+        <v>3</v>
       </c>
     </row>
     <row r="488" spans="1:2">
@@ -7052,7 +7084,7 @@
         <v>515</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="490" spans="1:2">
@@ -7060,7 +7092,7 @@
         <v>516</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="491" spans="1:2">
@@ -7068,7 +7100,7 @@
         <v>517</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
     </row>
     <row r="492" spans="1:2">
@@ -7076,7 +7108,7 @@
         <v>518</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>16</v>
+        <v>209</v>
       </c>
     </row>
     <row r="493" spans="1:2">
@@ -7092,7 +7124,7 @@
         <v>520</v>
       </c>
       <c r="B494" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="495" spans="1:2">
@@ -7100,7 +7132,7 @@
         <v>521</v>
       </c>
       <c r="B495" s="4" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="496" spans="1:2">
@@ -7108,7 +7140,7 @@
         <v>522</v>
       </c>
       <c r="B496" s="4" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="497" spans="1:2">
@@ -7116,7 +7148,7 @@
         <v>523</v>
       </c>
       <c r="B497" s="4" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
     </row>
     <row r="498" spans="1:2">
@@ -7124,7 +7156,7 @@
         <v>524</v>
       </c>
       <c r="B498" s="4" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="499" spans="1:2">
@@ -7132,7 +7164,7 @@
         <v>525</v>
       </c>
       <c r="B499" s="4" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="500" spans="1:2">
@@ -7140,7 +7172,7 @@
         <v>526</v>
       </c>
       <c r="B500" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="501" spans="1:2">
@@ -7148,7 +7180,7 @@
         <v>527</v>
       </c>
       <c r="B501" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="502" spans="1:2">
@@ -7156,7 +7188,7 @@
         <v>528</v>
       </c>
       <c r="B502" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="503" spans="1:2">
@@ -7164,7 +7196,7 @@
         <v>529</v>
       </c>
       <c r="B503" s="4" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
     </row>
     <row r="504" spans="1:2">
@@ -7172,7 +7204,7 @@
         <v>530</v>
       </c>
       <c r="B504" s="4" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -7180,7 +7212,7 @@
         <v>531</v>
       </c>
       <c r="B505" s="4" t="s">
-        <v>91</v>
+        <v>3</v>
       </c>
     </row>
     <row r="506" spans="1:2">
@@ -7188,7 +7220,7 @@
         <v>532</v>
       </c>
       <c r="B506" s="4" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
     </row>
     <row r="507" spans="1:2">
@@ -7196,7 +7228,7 @@
         <v>533</v>
       </c>
       <c r="B507" s="4" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="508" spans="1:2">
@@ -7204,7 +7236,7 @@
         <v>534</v>
       </c>
       <c r="B508" s="4" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="509" spans="1:2">
@@ -7212,7 +7244,7 @@
         <v>535</v>
       </c>
       <c r="B509" s="4" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
     </row>
     <row r="510" spans="1:2">
@@ -7220,7 +7252,7 @@
         <v>536</v>
       </c>
       <c r="B510" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="511" spans="1:2">
@@ -7228,7 +7260,7 @@
         <v>537</v>
       </c>
       <c r="B511" s="4" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
     </row>
     <row r="512" spans="1:2">
@@ -7236,7 +7268,7 @@
         <v>538</v>
       </c>
       <c r="B512" s="4" t="s">
-        <v>3</v>
+        <v>161</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -7244,7 +7276,7 @@
         <v>539</v>
       </c>
       <c r="B513" s="4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -7252,7 +7284,7 @@
         <v>540</v>
       </c>
       <c r="B514" s="4" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -7260,7 +7292,7 @@
         <v>541</v>
       </c>
       <c r="B515" s="4" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="516" spans="1:2">
@@ -7268,7 +7300,7 @@
         <v>542</v>
       </c>
       <c r="B516" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="517" spans="1:2">
@@ -7276,7 +7308,7 @@
         <v>543</v>
       </c>
       <c r="B517" s="4" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="518" spans="1:2">
@@ -7284,7 +7316,7 @@
         <v>544</v>
       </c>
       <c r="B518" s="4" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="519" spans="1:2">
@@ -7292,7 +7324,7 @@
         <v>545</v>
       </c>
       <c r="B519" s="4" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="520" spans="1:2">
@@ -7300,7 +7332,7 @@
         <v>546</v>
       </c>
       <c r="B520" s="4" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="521" spans="1:2">
@@ -7308,7 +7340,7 @@
         <v>547</v>
       </c>
       <c r="B521" s="4" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="522" spans="1:2">
@@ -7324,7 +7356,7 @@
         <v>549</v>
       </c>
       <c r="B523" s="4" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="524" spans="1:2">
@@ -7332,7 +7364,7 @@
         <v>550</v>
       </c>
       <c r="B524" s="4" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
     </row>
     <row r="525" spans="1:2">
@@ -7340,7 +7372,7 @@
         <v>551</v>
       </c>
       <c r="B525" s="4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="526" spans="1:2">
@@ -7348,7 +7380,7 @@
         <v>552</v>
       </c>
       <c r="B526" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="527" spans="1:2">
@@ -7356,7 +7388,7 @@
         <v>553</v>
       </c>
       <c r="B527" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="528" spans="1:2">
@@ -7364,7 +7396,7 @@
         <v>554</v>
       </c>
       <c r="B528" s="4" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="529" spans="1:2">
@@ -7372,7 +7404,7 @@
         <v>555</v>
       </c>
       <c r="B529" s="4" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="530" spans="1:2">
@@ -7380,7 +7412,7 @@
         <v>556</v>
       </c>
       <c r="B530" s="4" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
     </row>
     <row r="531" spans="1:2">
@@ -7388,7 +7420,7 @@
         <v>557</v>
       </c>
       <c r="B531" s="4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="532" spans="1:2">
@@ -7404,7 +7436,7 @@
         <v>559</v>
       </c>
       <c r="B533" s="4" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
     </row>
     <row r="534" spans="1:2">
@@ -7412,7 +7444,7 @@
         <v>560</v>
       </c>
       <c r="B534" s="4" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
     </row>
     <row r="535" spans="1:2">
@@ -7420,7 +7452,7 @@
         <v>561</v>
       </c>
       <c r="B535" s="4" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="536" spans="1:2">
@@ -7428,7 +7460,7 @@
         <v>562</v>
       </c>
       <c r="B536" s="4" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
     </row>
     <row r="537" spans="1:2">
@@ -7436,7 +7468,7 @@
         <v>563</v>
       </c>
       <c r="B537" s="4" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="538" spans="1:2">
@@ -7444,7 +7476,7 @@
         <v>564</v>
       </c>
       <c r="B538" s="4" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="539" spans="1:2">
@@ -7452,7 +7484,7 @@
         <v>565</v>
       </c>
       <c r="B539" s="4" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="540" spans="1:2">
@@ -7460,7 +7492,7 @@
         <v>566</v>
       </c>
       <c r="B540" s="4" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
     </row>
     <row r="541" spans="1:2">
@@ -7468,7 +7500,7 @@
         <v>567</v>
       </c>
       <c r="B541" s="4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="542" spans="1:2">
@@ -7484,7 +7516,7 @@
         <v>569</v>
       </c>
       <c r="B543" s="4" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
     </row>
     <row r="544" spans="1:2">
@@ -7492,7 +7524,7 @@
         <v>570</v>
       </c>
       <c r="B544" s="4" t="s">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="545" spans="1:2">
@@ -7508,7 +7540,7 @@
         <v>572</v>
       </c>
       <c r="B546" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="547" spans="1:2">
@@ -7516,7 +7548,7 @@
         <v>573</v>
       </c>
       <c r="B547" s="4" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="548" spans="1:2">
@@ -7524,7 +7556,7 @@
         <v>574</v>
       </c>
       <c r="B548" s="4" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
     </row>
     <row r="549" spans="1:2">
@@ -7532,7 +7564,7 @@
         <v>575</v>
       </c>
       <c r="B549" s="4" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="550" spans="1:2">
@@ -7540,7 +7572,7 @@
         <v>576</v>
       </c>
       <c r="B550" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="551" spans="1:2">
@@ -7556,7 +7588,7 @@
         <v>578</v>
       </c>
       <c r="B552" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="553" spans="1:2">
@@ -7564,7 +7596,7 @@
         <v>579</v>
       </c>
       <c r="B553" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="554" spans="1:2">
@@ -7572,7 +7604,7 @@
         <v>580</v>
       </c>
       <c r="B554" s="4" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="555" spans="1:2">
@@ -7580,7 +7612,7 @@
         <v>581</v>
       </c>
       <c r="B555" s="4" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="556" spans="1:2">
@@ -7588,7 +7620,7 @@
         <v>582</v>
       </c>
       <c r="B556" s="4" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="557" spans="1:2">
@@ -7596,7 +7628,7 @@
         <v>583</v>
       </c>
       <c r="B557" s="4" t="s">
-        <v>60</v>
+        <v>3</v>
       </c>
     </row>
     <row r="558" spans="1:2">
@@ -7604,7 +7636,7 @@
         <v>584</v>
       </c>
       <c r="B558" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="559" spans="1:2">
@@ -7612,7 +7644,7 @@
         <v>585</v>
       </c>
       <c r="B559" s="4" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
     </row>
     <row r="560" spans="1:2">
@@ -7620,7 +7652,7 @@
         <v>586</v>
       </c>
       <c r="B560" s="4" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="561" spans="1:2">
@@ -7636,7 +7668,7 @@
         <v>588</v>
       </c>
       <c r="B562" s="4" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="563" spans="1:2">
@@ -7644,7 +7676,7 @@
         <v>589</v>
       </c>
       <c r="B563" s="4" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="564" spans="1:2">
@@ -7652,7 +7684,7 @@
         <v>590</v>
       </c>
       <c r="B564" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="565" spans="1:2">
@@ -7660,7 +7692,7 @@
         <v>591</v>
       </c>
       <c r="B565" s="4" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
     </row>
     <row r="566" spans="1:2">
@@ -7668,7 +7700,7 @@
         <v>592</v>
       </c>
       <c r="B566" s="4" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="567" spans="1:2">
@@ -7676,7 +7708,7 @@
         <v>593</v>
       </c>
       <c r="B567" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="568" spans="1:2">
@@ -7684,7 +7716,7 @@
         <v>594</v>
       </c>
       <c r="B568" s="4" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="569" spans="1:2">
@@ -7692,7 +7724,7 @@
         <v>595</v>
       </c>
       <c r="B569" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="570" spans="1:2">
@@ -7708,7 +7740,7 @@
         <v>597</v>
       </c>
       <c r="B571" s="4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="572" spans="1:2">
@@ -7716,7 +7748,7 @@
         <v>598</v>
       </c>
       <c r="B572" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="573" spans="1:2">
@@ -7724,7 +7756,7 @@
         <v>599</v>
       </c>
       <c r="B573" s="4" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
     </row>
     <row r="574" spans="1:2">
@@ -7732,7 +7764,7 @@
         <v>600</v>
       </c>
       <c r="B574" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="575" spans="1:2">
@@ -7740,7 +7772,7 @@
         <v>601</v>
       </c>
       <c r="B575" s="4" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="576" spans="1:2">
@@ -7748,7 +7780,7 @@
         <v>602</v>
       </c>
       <c r="B576" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="577" spans="1:2">
@@ -7756,7 +7788,7 @@
         <v>603</v>
       </c>
       <c r="B577" s="4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="578" spans="1:2">
@@ -7764,7 +7796,7 @@
         <v>604</v>
       </c>
       <c r="B578" s="4" t="s">
-        <v>60</v>
+        <v>3</v>
       </c>
     </row>
     <row r="579" spans="1:2">
@@ -7772,7 +7804,7 @@
         <v>605</v>
       </c>
       <c r="B579" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="580" spans="1:2">
@@ -7780,7 +7812,7 @@
         <v>606</v>
       </c>
       <c r="B580" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="581" spans="1:2">
@@ -7788,7 +7820,7 @@
         <v>607</v>
       </c>
       <c r="B581" s="4" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="582" spans="1:2">
@@ -7796,7 +7828,7 @@
         <v>608</v>
       </c>
       <c r="B582" s="4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="583" spans="1:2">
@@ -7804,7 +7836,7 @@
         <v>609</v>
       </c>
       <c r="B583" s="4" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="584" spans="1:2">
@@ -7812,7 +7844,7 @@
         <v>610</v>
       </c>
       <c r="B584" s="4" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="585" spans="1:2">
@@ -7820,7 +7852,7 @@
         <v>611</v>
       </c>
       <c r="B585" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="586" spans="1:2">
@@ -7828,7 +7860,7 @@
         <v>612</v>
       </c>
       <c r="B586" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="587" spans="1:2">
@@ -7836,7 +7868,7 @@
         <v>613</v>
       </c>
       <c r="B587" s="4" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="588" spans="1:2">
@@ -7844,7 +7876,7 @@
         <v>614</v>
       </c>
       <c r="B588" s="4" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="589" spans="1:2">
@@ -7852,7 +7884,7 @@
         <v>615</v>
       </c>
       <c r="B589" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="590" spans="1:2">
@@ -7860,7 +7892,7 @@
         <v>616</v>
       </c>
       <c r="B590" s="4" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
     </row>
     <row r="591" spans="1:2">
@@ -7868,7 +7900,7 @@
         <v>617</v>
       </c>
       <c r="B591" s="4" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
     </row>
     <row r="592" spans="1:2">
@@ -7876,7 +7908,7 @@
         <v>618</v>
       </c>
       <c r="B592" s="4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="593" spans="1:2">
@@ -7884,7 +7916,7 @@
         <v>619</v>
       </c>
       <c r="B593" s="4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="594" spans="1:2">
@@ -7892,7 +7924,7 @@
         <v>620</v>
       </c>
       <c r="B594" s="4" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="595" spans="1:2">
@@ -7900,7 +7932,7 @@
         <v>621</v>
       </c>
       <c r="B595" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="596" spans="1:2">
@@ -7908,7 +7940,7 @@
         <v>622</v>
       </c>
       <c r="B596" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="597" spans="1:2">
@@ -7916,7 +7948,7 @@
         <v>623</v>
       </c>
       <c r="B597" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="598" spans="1:2">
@@ -7924,7 +7956,7 @@
         <v>624</v>
       </c>
       <c r="B598" s="4" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="599" spans="1:2">
@@ -7932,7 +7964,7 @@
         <v>625</v>
       </c>
       <c r="B599" s="4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="600" spans="1:2">
@@ -7940,7 +7972,7 @@
         <v>626</v>
       </c>
       <c r="B600" s="4" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="601" spans="1:2">
@@ -7948,6 +7980,54 @@
         <v>627</v>
       </c>
       <c r="B601" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="B602" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="B603" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="B604" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="B605" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="B606" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="B607" s="4" t="s">
         <v>8</v>
       </c>
     </row>

--- a/运单段码对照表.xlsx
+++ b/运单段码对照表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13605"/>
+    <workbookView windowWidth="28800" windowHeight="11805"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="640">
   <si>
     <t>运单号</t>
   </si>
@@ -1929,6 +1929,24 @@
   </si>
   <si>
     <t>JDM000002716722</t>
+  </si>
+  <si>
+    <t>JDM000004648942</t>
+  </si>
+  <si>
+    <t>JDM000004302515</t>
+  </si>
+  <si>
+    <t>JDM000003736095</t>
+  </si>
+  <si>
+    <t>JDM000002861416</t>
+  </si>
+  <si>
+    <t>JDM000001931730</t>
+  </si>
+  <si>
+    <t>JDM000003187445</t>
   </si>
 </sst>
 </file>
@@ -2695,7 +2713,14 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2889,25 +2914,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3168,7 +3193,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B607"/>
+  <dimension ref="A1:B619"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="26.125" customWidth="1"/>
@@ -8031,7 +8056,79 @@
         <v>8</v>
       </c>
     </row>
+    <row r="608" spans="1:2">
+      <c r="A608" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="B608" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="B609" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="B610" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="B611" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="B612" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="B613" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614" s="3"/>
+      <c r="B614" s="4"/>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615" s="3"/>
+      <c r="B615" s="4"/>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616" s="3"/>
+      <c r="B616" s="4"/>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617" s="3"/>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618" s="3"/>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619" s="3"/>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A$1:A$1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/运单段码对照表.xlsx
+++ b/运单段码对照表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11805"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3193,7 +3193,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B619"/>
+  <dimension ref="A1:B613"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="26.125" customWidth="1"/>
@@ -8061,7 +8061,7 @@
         <v>634</v>
       </c>
       <c r="B608" s="4" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
     </row>
     <row r="609" spans="1:2">
@@ -8085,7 +8085,7 @@
         <v>637</v>
       </c>
       <c r="B611" s="4" t="s">
-        <v>209</v>
+        <v>71</v>
       </c>
     </row>
     <row r="612" spans="1:2">
@@ -8103,27 +8103,6 @@
       <c r="B613" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="614" spans="1:2">
-      <c r="A614" s="3"/>
-      <c r="B614" s="4"/>
-    </row>
-    <row r="615" spans="1:2">
-      <c r="A615" s="3"/>
-      <c r="B615" s="4"/>
-    </row>
-    <row r="616" spans="1:2">
-      <c r="A616" s="3"/>
-      <c r="B616" s="4"/>
-    </row>
-    <row r="617" spans="1:2">
-      <c r="A617" s="3"/>
-    </row>
-    <row r="618" spans="1:2">
-      <c r="A618" s="3"/>
-    </row>
-    <row r="619" spans="1:2">
-      <c r="A619" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A$1:A$1048576">
